--- a/03_Outputs/Agua_Bosques_Turismo/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Agua_Bosques_Turismo/02_Demografia/demografia.xlsx
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="E14" s="81">
-        <v>9.10747221242821</v>
+        <v>9.1074722124282</v>
       </c>
       <c r="F14" s="83">
         <v>5.0928283119626</v>
